--- a/artfynd/A 32929-2024 artfynd.xlsx
+++ b/artfynd/A 32929-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119481712</v>
+        <v>119481519</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>95455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593776</v>
+        <v>593800</v>
       </c>
       <c r="R2" t="n">
-        <v>7035594</v>
+        <v>7035620</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119481519</v>
+        <v>119481712</v>
       </c>
       <c r="B3" t="n">
-        <v>95455</v>
+        <v>96862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593800</v>
+        <v>593776</v>
       </c>
       <c r="R3" t="n">
-        <v>7035620</v>
+        <v>7035594</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119481146</v>
+        <v>119482720</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Forsåsberget, Forsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593814</v>
+        <v>593748</v>
       </c>
       <c r="R9" t="n">
-        <v>7035616</v>
+        <v>7035558</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119482720</v>
+        <v>119481146</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,45 +1507,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Forsåsberget, Forsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593748</v>
+        <v>593814</v>
       </c>
       <c r="R10" t="n">
-        <v>7035558</v>
+        <v>7035616</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119481362</v>
+        <v>119482655</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,25 +2629,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593789</v>
+        <v>593760</v>
       </c>
       <c r="R21" t="n">
-        <v>7035617</v>
+        <v>7035551</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,22 +2707,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119482655</v>
+        <v>119481362</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593760</v>
+        <v>593789</v>
       </c>
       <c r="R22" t="n">
-        <v>7035551</v>
+        <v>7035617</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2809,12 +2809,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119480540</v>
+        <v>119480984</v>
       </c>
       <c r="B27" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,42 +3254,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Forsåsberget, Forsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593738</v>
+        <v>593822</v>
       </c>
       <c r="R27" t="n">
-        <v>7035512</v>
+        <v>7035603</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3319,6 +3314,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119480984</v>
+        <v>119480540</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,37 +3361,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Forsåsberget, Forsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>593822</v>
+        <v>593738</v>
       </c>
       <c r="R28" t="n">
-        <v>7035603</v>
+        <v>7035512</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3421,11 +3426,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På rönn</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 32929-2024 artfynd.xlsx
+++ b/artfynd/A 32929-2024 artfynd.xlsx
@@ -2311,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119481206</v>
+        <v>119480602</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2327,21 +2327,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593814</v>
+        <v>593743</v>
       </c>
       <c r="R18" t="n">
-        <v>7035616</v>
+        <v>7035495</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,22 +2401,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119480602</v>
+        <v>119481206</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,13 +2453,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593743</v>
+        <v>593814</v>
       </c>
       <c r="R19" t="n">
-        <v>7035495</v>
+        <v>7035616</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,12 +2503,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
